--- a/rover_platform_mbse/export/ROVER-A1-ROVER_HARDWARE_INTERFACE-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_HARDWARE_INTERFACE-SWRS-V-001.xlsx
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_HARDWARE_INTERFACE-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_HARDWARE_INTERFACE-SWRS-V-001.xlsx
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_HARDWARE_INTERFACE-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_HARDWARE_INTERFACE-SWRS-V-001.xlsx
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>The rover_hardware_interface shall publish rover_msgs/RoverDriverState on hardware_interface/rover_driver_state at driver_states_update_frequency (20 Hz) with QoS reliable, volatile, KeepLast(5), reporting per driver current, temperature, fault flags, data time-outs and comm_error, where comm_error is set when no Phidget telemetry callback arrived within driver_comm_timeout_ms (300 ms).</t>
+          <t>The rover_hardware_interface shall publish rover_msgs/RoverDriverState on hardware_interface/driver_state at driver_states_update_frequency (20 Hz) with QoS reliable, volatile, KeepLast(5), reporting per driver current, temperature, fault flags, data time-outs and comm_error, where comm_error is set when no Phidget telemetry callback arrived within driver_comm_timeout_ms (300 ms).</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
